--- a/Unity/Assets/Config/Excel/SceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SceneConfig.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11115" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="SceneConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="主城" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -38,10 +38,16 @@
     <t>地图类型</t>
   </si>
   <si>
+    <t>资源路径</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
     <t>MapSceneType</t>
+  </si>
+  <si>
+    <t>AssetPath</t>
   </si>
   <si>
     <t>int</t>
@@ -53,16 +59,7 @@
     <t>主城</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>荒漠领域</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>房间地块Demo</t>
+    <t>Lobby/Lobby</t>
   </si>
 </sst>
 </file>
@@ -75,30 +72,9 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -249,7 +225,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,25 +234,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149906918546098"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,12 +354,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -467,53 +419,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </left>
-      <right style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </right>
-      <top style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </top>
-      <bottom style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </left>
-      <right style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color theme="1" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -634,52 +545,61 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -688,117 +608,82 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1118,100 +1003,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A3:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="4" max="4" width="20.125" customWidth="1"/>
+    <col min="5" max="5" width="19.5" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+    <row r="3" s="1" customFormat="1" spans="3:6">
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+    <row r="4" s="1" customFormat="1" spans="3:6">
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" ht="14.25" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="5" s="1" customFormat="1" spans="3:6">
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>2</v>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="10">
-        <v>2</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>10</v>
-      </c>
+    <row r="7" spans="3:5">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="7">
-        <v>3</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>10</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/SceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/SceneConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Id</t>
   </si>
@@ -50,10 +50,13 @@
     <t>AssetPath</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
   <si>
     <t>主城</t>
@@ -744,13 +747,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1047,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -1060,13 +1056,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="3:5">
